--- a/data/export-final.xlsx
+++ b/data/export-final.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,7 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -47,8 +48,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,168 +418,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Acinetobacter baumannii NCTC 13301 (OXA-23 + OXA-51-like)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Candida albicans ATCC 90028 = CCM 8161</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Enterococcus faecalis ATCC 29212 = CCM 4224</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Enterococcus faecium 419/ANA </t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli 20574/C</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli ATCC 25922 = CCM 3954</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Escherichia coli CE5556 </t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli NCTC 13846 = CCM 8874 (COL R)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Klebsiella pneumoniae NCTC 13438 (KPC-3)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Klebsiella pneumoniae NCTC 13443 (NDM-1)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Proteus mirabilis 16585/B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Pseudomonas aeruginosa ATCC 27853 = CCM 3955</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pseudomonas aeruginosa R</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus aureus 4591</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus aureus ATCC 29213 = CCM 4223</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus epidermidis CCM 7221</t>
         </is>
       </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>I76DR_1037P1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -584,7 +608,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_231P1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,6 +682,11 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -666,7 +695,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_233P1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -740,6 +769,11 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -748,7 +782,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_235P1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -822,6 +856,11 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -830,7 +869,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_240P1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -840,14 +879,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -855,24 +894,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -895,15 +934,20 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -912,15 +956,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
+          <t>I76NS_241P1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -982,6 +1026,11 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -998,168 +1047,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Acinetobacter baumannii NCTC 13301 (OXA-23 + OXA-51-like)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Candida albicans ATCC 90028 = CCM 8161</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Enterococcus faecalis ATCC 29212 = CCM 4224</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Enterococcus faecium 419/ANA </t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli 20574/C</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli ATCC 25922 = CCM 3954</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Escherichia coli CE5556 </t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Escherichia coli NCTC 13846 = CCM 8874 (COL R)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Klebsiella pneumoniae NCTC 13438 (KPC-3)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Klebsiella pneumoniae NCTC 13443 (NDM-1)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Proteus mirabilis 16585/B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Pseudomonas aeruginosa ATCC 27853 = CCM 3955</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pseudomonas aeruginosa R</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus aureus 4591</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus aureus ATCC 29213 = CCM 4223</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Staphylococcus epidermidis CCM 7221</t>
         </is>
       </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>I76DR_1037P1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1168,7 +1237,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_231P1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1242,6 +1311,11 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -1250,7 +1324,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_233P1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1324,6 +1398,11 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -1332,7 +1411,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_235P1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1406,6 +1485,11 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>
@@ -1414,24 +1498,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>&gt;128</t>
+          <t>I76NS_240P1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -1439,24 +1523,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -1469,25 +1553,30 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1496,15 +1585,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
+          <t>I76NS_241P1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -1566,6 +1655,11 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>&gt;128</t>
         </is>

--- a/data/export-final.xlsx
+++ b/data/export-final.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -705,64 +705,64 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1277,14 +1277,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2180,49 +2180,49 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2310,11 +2310,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>1</t>
@@ -2337,7 +2333,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2462,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2529,7 +2525,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3677,7 +3673,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3882,7 +3878,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3934,7 +3930,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4166,7 +4162,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4248,49 +4244,49 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -4298,7 +4294,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4335,49 +4331,49 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>&gt;128</t>
@@ -4390,7 +4386,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4487,7 +4483,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4534,7 +4530,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4559,7 +4555,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4704,7 +4700,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4729,7 +4725,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4747,11 +4743,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4826,12 +4818,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4990,7 +4982,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5092,12 +5084,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5450,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5483,7 +5475,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5546,7 +5538,7 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5576,7 +5568,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5606,7 +5598,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5638,57 +5630,57 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5785,7 +5777,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5814,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5867,7 +5859,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5894,7 +5886,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6166,7 +6158,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6248,62 +6240,62 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>≤0,06</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6332,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6375,7 +6367,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6427,7 +6419,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6457,7 +6449,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6504,67 +6496,67 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>≤0,06</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6629,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6684,7 +6676,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6694,7 +6686,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6771,7 +6763,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6806,7 +6798,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6839,62 +6831,62 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>0.2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0.1</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6971,7 +6963,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7008,7 +7000,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7028,17 +7020,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7165,7 +7157,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -7197,14 +7189,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -7212,7 +7204,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7237,7 +7229,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7339,7 +7331,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7364,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7417,12 +7409,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7476,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7494,7 +7486,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7531,7 +7523,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7541,7 +7533,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7608,7 +7600,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7678,12 +7670,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>≤ 0,06</t>
         </is>
       </c>
     </row>
@@ -7700,12 +7692,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7750,7 +7742,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -7770,7 +7762,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>≤ 0,06</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7789,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7857,7 +7849,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>≤ 0,06</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7867,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7930,7 +7922,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -8417,7 +8409,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8462,7 +8454,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -8477,12 +8469,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8551,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -8586,7 +8578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -8636,14 +8628,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
@@ -8656,7 +8648,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8685,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8760,7 +8752,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8780,7 +8772,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8820,12 +8812,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -8862,7 +8854,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8954,12 +8946,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8974,24 +8966,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>2</t>
@@ -9004,7 +8996,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -9021,44 +9013,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>2</t>
@@ -9086,7 +9078,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -9173,12 +9165,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9257,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9344,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9426,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -9472,7 +9464,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9517,12 +9509,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9618,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9733,7 +9725,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -9773,7 +9765,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -9974,22 +9966,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -10004,7 +9996,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -10061,22 +10053,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10111,7 +10103,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -10173,7 +10165,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10327,7 +10319,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10377,7 +10369,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -10392,7 +10384,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10435,7 +10427,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -11763,12 +11755,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -11815,34 +11807,34 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>4</t>
@@ -11850,12 +11842,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12006,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -12107,7 +12099,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -12134,59 +12126,59 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>2</t>
@@ -12199,7 +12191,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12208,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -12343,7 +12335,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -12420,7 +12412,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -12492,7 +12484,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12527,17 +12519,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -12565,7 +12557,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12585,7 +12577,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -12642,29 +12634,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>1</t>
@@ -12677,7 +12669,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -12697,7 +12689,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -12712,7 +12704,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -12749,7 +12741,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -12784,7 +12776,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -12881,7 +12873,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -13339,19 +13331,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>2</t>
@@ -13364,12 +13356,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -13404,7 +13396,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -13457,7 +13449,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -13467,7 +13459,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>&gt;128</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -13569,17 +13561,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -13631,7 +13623,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -13641,7 +13633,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -13703,7 +13695,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -13753,7 +13745,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13767,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13830,7 +13822,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -13872,7 +13864,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -13917,7 +13909,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -13950,12 +13942,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -14027,7 +14019,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14047,7 +14039,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -14072,7 +14064,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -14114,7 +14106,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14134,57 +14126,57 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>&gt;128</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14213,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -14303,7 +14295,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -14318,7 +14310,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -14385,12 +14377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -14471,11 +14463,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>0.2</t>
@@ -14513,7 +14501,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -14565,7 +14553,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14575,7 +14563,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -14600,7 +14588,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -14652,52 +14640,52 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -14720,62 +14708,62 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>0.2</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0.1</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -14812,7 +14800,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14852,7 +14840,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -14909,57 +14897,57 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>0.2</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -15006,7 +14994,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -15026,19 +15014,15 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
+          <t>&gt;128</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>1</t>
@@ -15078,14 +15062,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -15093,24 +15077,24 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>8</t>
@@ -15118,7 +15102,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -15165,7 +15149,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -15205,12 +15189,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -15220,7 +15204,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -15243,67 +15227,67 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>0.2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15309,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -15365,7 +15349,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>64</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15375,7 +15359,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -15390,7 +15374,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15461,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15543,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -15581,7 +15565,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15641,7 +15625,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -15708,7 +15692,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -15738,7 +15722,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15740,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -15811,7 +15795,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
